--- a/other/civil_litigation_knowledge_quiz.xlsx
+++ b/other/civil_litigation_knowledge_quiz.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1215,85 +1215,187 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>civil_litigation_important_question_answer_choices</t>
+          <t>civil_litigation_knowledge_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>correct_-_incorrect</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Correct - Incorrect</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>civil_litigation_important_question_answer_choices</t>
+          <t>civil_litigation_important_question_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_answered</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Not Answered</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>civil_litigation_knowledge_result_choices</t>
+          <t>civil_litigation_important_question_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>passed_-_failed</t>
+          <t>not_important</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Passed - Failed</t>
+          <t>Not Important</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>civil_litigation_knowledge_result_choices</t>
+          <t>civil_litigation_important_question_answer_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>correct_-_incorrect</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Correct - Incorrect</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>civil_litigation_important_question_answer_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>not_answered</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Not Answered</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>civil_litigation_important_result_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>very_important</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Very Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>civil_litigation_important_result_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>not_important</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not Important</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>civil_litigation_knowledge_result_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>passed_-_failed</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Passed - Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>civil_litigation_knowledge_result_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>civil_litigation_result_choices</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>passed_-_failed</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Passed - Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>civil_litigation_result_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
